--- a/toy-rulebooks/a1-effortless-init-sample/xlsx/a1-effortless-init-sample.xlsx
+++ b/toy-rulebooks/a1-effortless-init-sample/xlsx/a1-effortless-init-sample.xlsx
@@ -9,14 +9,14 @@
     <sheet name="_original_json" sheetId="2" r:id="rId3" state="hidden"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HelloWhos!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HelloWhos!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>HelloWhoId</t>
   </si>
@@ -27,9 +27,6 @@
     <t>Introduction</t>
   </si>
   <si>
-    <t>IsBob</t>
-  </si>
-  <si>
     <t>world</t>
   </si>
   <si>
@@ -39,13 +36,7 @@
     <t>bob</t>
   </si>
   <si>
-    <t>Bobby</t>
-  </si>
-  <si>
-    <t>bob2</t>
-  </si>
-  <si>
-    <t>Robby</t>
+    <t>Bob</t>
   </si>
   <si>
     <t>everyone</t>
@@ -60,55 +51,18 @@
   "HelloWhos": {
     "Description": "The smallest complete rulebook: an id, a display name, and a rule that derives a greeting from it.",
     "schema": [
-      {
-        "name": "HelloWhoId",
-        "datatype": "string",
-        "type": "raw",
-        "description": "The unique identifier for the HelloWho entity.",
-        "nullable": false
-      },
-      {
-        "name": "Name",
-        "datatype": "string",
-        "type": "raw",
-        "nullable": false
-      },
-      {
-        "name": "Introduction",
-        "datatype": "string",
-        "type": "calculated",
-        "nullable": false,
-        "formula": "=\"Hi, \" &amp; {{Name}} &amp; \".\""
-      },
-      {"name": "IsBob", "datatype": "boolean", "formula": "=OR({{Name}}=\"Bob\", {{Name}}=\"Bobby\", {{Name}}=\"Robert\")", "type": "calculated"}
+      { "name": "HelloWhoId", "datatype": "string", "type": "raw", "nullable": false },
+      { "name": "Name", "datatype": "string", "type": "raw", "nullable": false },
+      { "name": "Introduction", "datatype": "string", "type": "calculated", "nullable": false, "formula": "=\"Hello \" &amp; {{Name}} &amp; \"!!!\"" }
     ],
     "data": [
-      {
-        "HelloWhoId": "world",
-        "Name": "World",
-        "Introduction": "Hi, World.",
-        "IsBob": false
-      },
-      {
-        "HelloWhoId": "bob",
-        "Name": "Bobby",
-        "Introduction": "Hi, Bobby.",
-        "IsBob": true
-      },      {
-        "HelloWhoId": "bob2",
-        "Name": "Robby",
-        "Introduction": "Hi, Robby.",
-        "IsBob": false
-      },
-      {
-        "HelloWhoId": "everyone",
-        "Name": "Everyone",
-        "Introduction": "Hi, Everyone.",
-        "IsBob": false
-      }
+      { "HelloWhoId": "world", "Name": "World", "Introduction": "Hello World!!!" },
+      { "HelloWhoId": "bob", "Name": "Bob", "Introduction": "Hello Bob!!!" },
+      { "HelloWhoId": "everyone", "Name": "Everyone", "Introduction": "Hello Everyone!!!" }
     ]
   }
-}</t>
+}
+</t>
   </si>
 </sst>
 </file>
@@ -178,13 +132,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.443378448486328" customWidth="1"/>
     <col min="2" max="2" width="17.443378448486328" customWidth="1"/>
-    <col min="3" max="3" width="17.443378448486328" customWidth="1"/>
-    <col min="4" max="4" width="17.443378448486328" customWidth="1"/>
+    <col min="3" max="3" width="17.62145233154297" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -197,76 +150,45 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="3" t="str">
-        <f>"Hi, " &amp; B2 &amp; "."</f>
-        <v>Hi, World.</v>
-      </c>
-      <c r="D2" s="3" t="b">
-        <f>OR(B2="Bob", B2="Bobby", B2="Robert")</f>
-        <v>0</v>
+        <f>"Hello " &amp; B2 &amp; "!!!"</f>
+        <v>Hello World!!!</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="3" t="str">
-        <f>"Hi, " &amp; B3 &amp; "."</f>
-        <v>Hi, Bobby.</v>
-      </c>
-      <c r="D3" s="3" t="b">
-        <f>OR(B3="Bob", B3="Bobby", B3="Robert")</f>
-        <v>1</v>
+        <f>"Hello " &amp; B3 &amp; "!!!"</f>
+        <v>Hello Bob!!!</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="C4" s="3" t="str">
-        <f>"Hi, " &amp; B4 &amp; "."</f>
-        <v>Hi, Robby.</v>
-      </c>
-      <c r="D4" s="3" t="b">
-        <f>OR(B4="Bob", B4="Bobby", B4="Robert")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3" t="str">
-        <f>"Hi, " &amp; B5 &amp; "."</f>
-        <v>Hi, Everyone.</v>
-      </c>
-      <c r="D5" s="3" t="b">
-        <f>OR(B5="Bob", B5="Bobby", B5="Robert")</f>
-        <v>0</v>
+        <f>"Hello " &amp; B4 &amp; "!!!"</f>
+        <v>Hello Everyone!!!</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:C1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -278,7 +200,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
